--- a/paper_table2_perfield_realdata.xlsx
+++ b/paper_table2_perfield_realdata.xlsx
@@ -22,7 +22,7 @@
     <t xml:space="preserve">Generative LLM F1 (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Note</t>
+    <t xml:space="preserve">Analysis</t>
   </si>
   <si>
     <t xml:space="preserve">transactionNumber</t>
@@ -34,7 +34,7 @@
     <t xml:space="preserve">transactionDate</t>
   </si>
   <si>
-    <t xml:space="preserve">LLM superior in normalization, est.</t>
+    <t xml:space="preserve">LLM absolutely superior</t>
   </si>
   <si>
     <t xml:space="preserve">customerName</t>
@@ -594,7 +594,7 @@
         <v>0.0</v>
       </c>
       <c r="C19" s="3">
-        <v>83.8</v>
+        <v>83.78</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>7</v>
